--- a/Tasks/Input/EmployeeData.xlsx
+++ b/Tasks/Input/EmployeeData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\Admin\OneDrive - StayAhead\Documents\Demo_Sruthy\Tasks\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_35F90A63D408C93C270E521250FB60335BF91298" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30098756-3A82-4850-B5CC-F8BC3F04E945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
   <si>
     <t>First Name</t>
   </si>
@@ -124,15 +124,12 @@
     <t>Canadian</t>
   </si>
   <si>
+    <t>O+</t>
+  </si>
+  <si>
     <t>Daniel_Thompson.pdf</t>
   </si>
   <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>Failed after 2 attempts: Employee creation returned False</t>
-  </si>
-  <si>
     <t>Emily</t>
   </si>
   <si>
@@ -161,9 +158,6 @@
   </si>
   <si>
     <t>Spanish</t>
-  </si>
-  <si>
-    <t>O-</t>
   </si>
   <si>
     <t>James_Martinez.pdf</t>
@@ -193,17 +187,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -218,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -233,13 +222,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -588,7 +570,7 @@
     <col min="9" max="9" width="21.140625" customWidth="1"/>
     <col min="10" max="10" width="11.85546875" customWidth="1"/>
     <col min="11" max="11" width="56.85546875" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -697,50 +679,46 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="4">
         <v>33187</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6" t="s">
+      <c r="H4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="I4" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>25</v>
@@ -752,30 +730,24 @@
         <v>35100</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>15</v>
@@ -786,17 +758,9 @@
       <c r="G6" s="4">
         <v>33499</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
